--- a/data/gated_research.xlsx
+++ b/data/gated_research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO44" headerRowCount="1">
-  <autoFilter ref="A1:CO44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO29" headerRowCount="1">
+  <autoFilter ref="A1:CO29"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$44)</f>
+        <f>COUNTA('Picks'!$A$2:$A$29)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$44,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$44,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")+COUNTIFS('Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$44,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$29,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"win")/(COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"win")+COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")/(COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"win")+COUNTIFS('Picks'!$BX$2:$BX$29,"&gt;0",'Picks'!$V$2:$V$29,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$44)/SUM('Picks'!$BX$2:$BX$44),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$29)/SUM('Picks'!$BX$2:$BX$29),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$44)</f>
+        <f>SUM('Picks'!$BY$2:$BY$29)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$44,"&lt;&gt;",'Picks'!$AB$2:$AB$44),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$29,"&lt;&gt;",'Picks'!$AB$2:$AB$29),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$44,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$44,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$44,'Picks'!$AM$2:$AM$44,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$29,'Picks'!$AM$2:$AM$29,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$44,'Picks'!$H$2:$H$44,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$44,'Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A14,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$44,'Picks'!$H$2:$H$44,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$44,'Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A15,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled",'Picks'!$V$2:$V$29,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$44,'Picks'!$H$2:$H$44,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$29,'Picks'!$H$2:$H$29,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$44,'Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$29,'Picks'!$H$2:$H$29,$A16,'Picks'!$U$2:$U$29,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO44"/>
+  <dimension ref="A1:CO29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2481,18 +2481,32 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y5" s="25" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>1.5487</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:55.837413Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-nve-exmana-2026-07-26).</t>
@@ -2742,18 +2756,32 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:57.201845Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-gls-thg-2026-07-26).</t>
@@ -2766,7 +2794,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -3003,18 +3031,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:52:58.627121Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-lil-cla-2026-07-26).</t>
@@ -3027,7 +3069,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3447,37 +3489,37 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>1a4eefc540094895</t>
+          <t>04eaa9b94d3542cb</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T20:00:00Z</t>
+          <t>2026-07-26T14:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>60465</t>
+          <t>61440</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3497,49 +3539,63 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-138</v>
+        <v>100</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.724638</v>
+        <v>2</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.5</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.723066</v>
+        <v>0.769302</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.143234</v>
+        <v>0.269302</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:53:02.090518Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-lol-tl-c9-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-sta-lc-2026-07-26).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3549,7 +3605,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3580,32 +3636,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3623,7 +3679,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3633,12 +3689,12 @@
       </c>
       <c r="BC9" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3653,12 +3709,12 @@
       </c>
       <c r="BG9" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:14.812794Z</t>
+          <t>2026-07-26T12:49:44.422167Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3668,13 +3724,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-138</v>
+        <v>100</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.724638</v>
+        <v>2</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3708,37 +3764,37 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>b26fb366a5904bbc</t>
+          <t>a2203ec652454349</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T23:00:00Z</t>
+          <t>2026-07-26T14:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>60600</t>
+          <t>61033</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3758,49 +3814,63 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-133</v>
+        <v>-117</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.854701</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.539171</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.543543</v>
+        <v>0.518471</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>-0.027272</v>
+        <v>-0.0207</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S10" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T10" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:53:03.627722Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-lol-sr-dsg-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-sparta-atr-2026-07-26).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3810,7 +3880,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -3841,32 +3911,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3884,7 +3954,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -3894,12 +3964,12 @@
       </c>
       <c r="BC10" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -3914,12 +3984,12 @@
       </c>
       <c r="BG10" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:15.656044Z</t>
+          <t>2026-07-26T12:49:45.204211Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -3929,13 +3999,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-133</v>
+        <v>-117</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.854701</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.539171</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -3969,37 +4039,37 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>127655a8fb0d4d8e</t>
+          <t>caef081f30c24894</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T06:00:00Z</t>
+          <t>2026-07-26T15:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>60701</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4019,49 +4089,63 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>108</v>
+        <v>-178</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>2.08</v>
+        <v>1.561798</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.640288</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.811601</v>
+        <v>0.702966</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.330832</v>
+        <v>0.062678</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="S11" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>1.1236</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:53:04.985644Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-bfx-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-wc-mglz-2026-07-26).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4102,32 +4186,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>TheMongolz</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>BNK FEARX</t>
+          <t>Wildcard</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4145,7 +4229,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4155,12 +4239,12 @@
       </c>
       <c r="BC11" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4175,12 +4259,12 @@
       </c>
       <c r="BG11" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:16.441993Z</t>
+          <t>2026-07-26T12:49:46.102307Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4190,13 +4274,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>108</v>
+        <v>-178</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>2.08</v>
+        <v>1.561798</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.640288</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4230,37 +4314,37 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>7bced9b85b5d472d</t>
+          <t>59899b82acff46b4</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T06:45:00Z</t>
+          <t>2026-07-26T15:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>60706</t>
+          <t>61671</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4270,7 +4354,7 @@
       </c>
       <c r="I12" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -4280,49 +4364,63 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-170</v>
+        <v>178</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.78</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.359712</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.608349</v>
+        <v>0.786851</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>-0.021281</v>
+        <v>0.427139</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:53:06.560009Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-lol-dk-hle-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-odk-ldp-2026-07-26).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4363,32 +4461,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>largadosypelados</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>ODDIK</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4406,7 +4504,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4416,12 +4514,12 @@
       </c>
       <c r="BC12" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4436,12 +4534,12 @@
       </c>
       <c r="BG12" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:17.204873Z</t>
+          <t>2026-07-26T12:49:46.942100Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4451,13 +4549,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-170</v>
+        <v>178</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.78</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.359712</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4491,37 +4589,37 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>6d6407f0f4a94e69</t>
+          <t>40692918b0c94676</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T07:30:00Z</t>
+          <t>2026-07-26T16:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>60707</t>
+          <t>61948</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4531,7 +4629,7 @@
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J13" s="25" t="n"/>
@@ -4541,20 +4639,20 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.469484</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.7097250000000001</v>
+        <v>0.665479</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.339355</v>
+        <v>0.195995</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>100</v>
@@ -4564,7 +4662,7 @@
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U13" s="24" t="inlineStr">
@@ -4583,7 +4681,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-lol-kt-gen-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-mgc-nip-2026-07-26).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4624,32 +4722,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Gen.G</t>
+          <t>NIP</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>KT Rolster</t>
+          <t>magic</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4667,7 +4765,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4677,12 +4775,12 @@
       </c>
       <c r="BC13" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4697,12 +4795,12 @@
       </c>
       <c r="BG13" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:17.997008Z</t>
+          <t>2026-07-26T12:49:49.664310Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4712,13 +4810,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.469484</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -4752,37 +4850,37 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ed453bb5936c41fa</t>
+          <t>18212168114f4d40</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:13.208687Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:00:00Z</t>
+          <t>2026-07-26T17:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>60708</t>
+          <t>62237</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>CS2</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -4802,30 +4900,30 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.6818</v>
+        <v>0.700097</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.041512</v>
+        <v>0.08032499999999999</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="S14" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U14" s="24" t="inlineStr">
@@ -4844,7 +4942,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-t1a-nsea-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-hon-pg-2026-07-26).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -4885,32 +4983,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Esports Academy</t>
+          <t>Privateer Gaming</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>T1 Academy</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -4928,7 +5026,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -4938,12 +5036,12 @@
       </c>
       <c r="BC14" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -4958,12 +5056,12 @@
       </c>
       <c r="BG14" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>cs2-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:18.841768Z</t>
+          <t>2026-07-26T12:49:51.560831Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -4973,13 +5071,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5013,37 +5111,37 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>3e60a809243f4bee</t>
+          <t>e7c15658496b44c8</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T12:50:45.242095Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:15:00Z</t>
+          <t>2026-07-26T15:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>60713</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>LOL</t>
+          <t>VALORANT</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5063,49 +5161,63 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-178</v>
+        <v>156</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.56</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.390625</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.506725</v>
+        <v>0.7726229999999999</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>-0.133563</v>
+        <v>0.381998</v>
       </c>
       <c r="R15" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T15" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U15" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-26T17:53:13.868406Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-dk-t1-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-bbl-navi-2026-07-26).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5115,7 +5227,7 @@
       </c>
       <c r="AG15" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH15" s="24" t="n"/>
@@ -5146,32 +5258,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>BBL Esports</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5189,7 +5301,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5199,12 +5311,12 @@
       </c>
       <c r="BC15" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
+          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5219,12 +5331,12 @@
       </c>
       <c r="BG15" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v4</t>
+          <t>valorant-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:19.622422Z</t>
+          <t>2026-07-26T12:50:32.723645Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5234,13 +5346,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-178</v>
+        <v>156</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.56</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.390625</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5274,22 +5386,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>81b9a041f84244d4</t>
+          <t>6d72718c5c2642ba</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:00:00Z</t>
+          <t>2026-07-26T20:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>60465</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5299,12 +5411,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5324,23 +5436,23 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>133</v>
+        <v>-144</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>2.33</v>
+        <v>1.694444</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.590164</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.912307</v>
+        <v>0.723066</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.483122</v>
+        <v>0.132902</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>2</v>
@@ -5366,7 +5478,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-lol-hle-krx-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-lol-tl-c9-2026-07-26).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5407,32 +5519,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Cloud9</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>Hanwha Life Esports</t>
+          <t>Team Liquid</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5485,7 +5597,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:20.448813Z</t>
+          <t>2026-07-26T18:26:40.383810Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5495,13 +5607,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>133</v>
+        <v>-144</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>2.33</v>
+        <v>1.694444</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.590164</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5535,22 +5647,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>94b7bff372e04cef</t>
+          <t>b7b287b0f2f743df</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T09:45:00Z</t>
+          <t>2026-07-27T06:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>60723</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5560,12 +5672,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5575,7 +5687,7 @@
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J17" s="25" t="n"/>
@@ -5585,20 +5697,20 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>-163</v>
+        <v>-108</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.925926</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.519231</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.865659</v>
+        <v>0.811601</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.245887</v>
+        <v>0.29237</v>
       </c>
       <c r="R17" s="26" t="n">
         <v>100</v>
@@ -5627,7 +5739,7 @@
       <c r="AD17" s="24" t="n"/>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-lol-t1-ns-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-lol-bfx-gen-2026-07-27).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -5668,32 +5780,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Nongshim Red Force</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -5746,7 +5858,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:21.212140Z</t>
+          <t>2026-07-26T18:26:41.407259Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -5756,13 +5868,13 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>-163</v>
+        <v>-108</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.925926</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.519231</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
@@ -5796,22 +5908,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>7018021a5db841a6</t>
+          <t>c1c09b0be2e842ea</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:00:00Z</t>
+          <t>2026-07-27T07:30:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>60724</t>
+          <t>60707</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -5821,12 +5933,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -5846,23 +5958,23 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>-223</v>
+        <v>122</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.22</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.45045</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.654791</v>
+        <v>0.7097250000000001</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>-0.035611</v>
+        <v>0.259275</v>
       </c>
       <c r="R18" s="26" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="S18" s="29" t="n">
         <v>2</v>
@@ -5888,7 +6000,7 @@
       <c r="AD18" s="24" t="n"/>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-lol-genga-foxy-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-kt-gen-2026-07-27).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -5929,32 +6041,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>BNK FearX Youth</t>
+          <t>Gen.G</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Global Academy</t>
+          <t>KT Rolster</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6007,7 +6119,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:22.005575Z</t>
+          <t>2026-07-26T18:26:42.528294Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6017,13 +6129,13 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>-223</v>
+        <v>122</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.22</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.45045</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
@@ -6057,22 +6169,22 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>b1f313695cc1423a</t>
+          <t>177741e1657f4e43</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T10:30:00Z</t>
+          <t>2026-07-27T08:00:00Z</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>60725</t>
+          <t>60708</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6082,12 +6194,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6097,7 +6209,7 @@
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J19" s="25" t="n"/>
@@ -6107,23 +6219,23 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>194</v>
+        <v>-178</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>2.94</v>
+        <v>1.561798</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.640288</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.803091</v>
+        <v>0.6818</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.462955</v>
+        <v>0.041512</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="S19" s="29" t="n">
         <v>2</v>
@@ -6149,7 +6261,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-bro-dk-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-t1a-nsea-2026-07-27).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6190,32 +6302,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Dplus KIA</t>
+          <t>Nongshim Esports Academy</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>HANJIN BRION</t>
+          <t>T1 Academy</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6268,7 +6380,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:22.804506Z</t>
+          <t>2026-07-26T18:26:43.057913Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6278,13 +6390,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>194</v>
+        <v>-178</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>2.94</v>
+        <v>1.561798</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.640288</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6318,22 +6430,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>e36dbb13e49c4780</t>
+          <t>9329e4844a654b7e</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T11:15:00Z</t>
+          <t>2026-07-27T09:00:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>60734</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6343,12 +6455,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6368,20 +6480,20 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>-186</v>
+        <v>113</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.13</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.469484</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.885173</v>
+        <v>0.912307</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.234823</v>
+        <v>0.442823</v>
       </c>
       <c r="R20" s="26" t="n">
         <v>100</v>
@@ -6410,7 +6522,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-lol-t1-dns-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-lol-hle-krx-2026-07-27).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6451,32 +6563,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>DN SOOPers</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>Hanwha Life Esports</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6529,7 +6641,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:23.643887Z</t>
+          <t>2026-07-26T18:26:44.171133Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -6539,13 +6651,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>-186</v>
+        <v>113</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.13</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.469484</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -6579,22 +6691,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>aba12aad7a534a95</t>
+          <t>92458ed501d049b4</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:32.359065Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T21:00:00Z</t>
+          <t>2026-07-27T09:45:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>61044</t>
+          <t>60723</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -6604,12 +6716,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -6629,23 +6741,23 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>-233</v>
+        <v>-203</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.492611</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.669967</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.712884</v>
+        <v>0.865659</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.013184</v>
+        <v>0.195692</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S21" s="29" t="n">
         <v>2</v>
@@ -6671,7 +6783,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-lol-t1-ns-2026-07-27).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -6712,32 +6824,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>Ei Nerd Esports</t>
+          <t>Nongshim Red Force</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>paiN Gaming Academy</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -6790,7 +6902,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:28.530374Z</t>
+          <t>2026-07-26T18:26:44.707658Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -6800,13 +6912,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>-233</v>
+        <v>-203</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.492611</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.669967</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -6840,37 +6952,37 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>8f8ef4f76b2d4f5a</t>
+          <t>f69834df448c4f39</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T14:00:00Z</t>
+          <t>2026-07-27T10:30:00Z</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>61030</t>
+          <t>60725</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -6880,7 +6992,7 @@
       </c>
       <c r="I22" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J22" s="25" t="n"/>
@@ -6890,30 +7002,30 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>-233</v>
+        <v>194</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.94</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.340136</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.603297</v>
+        <v>0.803091</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>-0.096403</v>
+        <v>0.462955</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U22" s="24" t="inlineStr">
@@ -6932,7 +7044,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-inox-g2a-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-lol-bro-dk-2026-07-27).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -6973,32 +7085,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Dplus KIA</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>HANJIN BRION</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7016,7 +7128,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7026,12 +7138,12 @@
       </c>
       <c r="BC22" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7046,12 +7158,12 @@
       </c>
       <c r="BG22" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:42.821812Z</t>
+          <t>2026-07-26T18:26:45.912908Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7061,13 +7173,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>-233</v>
+        <v>194</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.94</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.340136</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7101,37 +7213,37 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>04eaa9b94d3542cb</t>
+          <t>6838161859c1499f</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:26:52.555147Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T14:00:00Z</t>
+          <t>2026-07-27T21:00:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>61440</t>
+          <t>61044</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>CS2</t>
+          <t>LOL</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7151,30 +7263,30 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>100</v>
+        <v>-233</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>2</v>
+        <v>1.429185</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.5</v>
+        <v>0.6997</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.769302</v>
+        <v>0.712884</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.269302</v>
+        <v>0.013184</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S23" s="29" t="n">
         <v>2</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="U23" s="24" t="inlineStr">
@@ -7193,7 +7305,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-sta-lc-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-pnga-nerd-2026-07-27).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7234,32 +7346,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Ei Nerd Esports</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>paiN Gaming Academy</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7277,7 +7389,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7287,12 +7399,12 @@
       </c>
       <c r="BC23" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>35087e828a0053011a97024de693e2ee7eb80eb03024c91d28d254de09d93778</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7307,12 +7419,12 @@
       </c>
       <c r="BG23" s="24" t="inlineStr">
         <is>
-          <t>cs2-tiered-elo-v4</t>
+          <t>lol-tiered-elo-v4</t>
         </is>
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:44.422167Z</t>
+          <t>2026-07-26T18:26:50.385656Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7322,13 +7434,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>100</v>
+        <v>-233</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>2</v>
+        <v>1.429185</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.5</v>
+        <v>0.6997</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7362,22 +7474,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>a2203ec652454349</t>
+          <t>c35f96acd12c4363</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T14:00:00Z</t>
+          <t>2026-07-27T08:00:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>61033</t>
+          <t>60702</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7387,12 +7499,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7402,7 +7514,7 @@
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -7412,26 +7524,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-117</v>
+        <v>163</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.63</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.380228</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.518471</v>
+        <v>0.607321</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>-0.0207</v>
+        <v>0.227093</v>
       </c>
       <c r="R24" s="26" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -7454,7 +7566,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-sparta-atr-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-erx-ent-2026-07-27).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7495,32 +7607,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -7573,7 +7685,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:45.204211Z</t>
+          <t>2026-07-26T18:27:02.006109Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7583,13 +7695,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-117</v>
+        <v>163</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.63</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.380228</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -7623,22 +7735,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>caef081f30c24894</t>
+          <t>03db4a92938042dd</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T15:00:00Z</t>
+          <t>2026-07-27T11:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>61219</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -7648,12 +7760,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -7663,7 +7775,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -7673,23 +7785,23 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.588235</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.62963</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.702966</v>
+        <v>0.736846</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.062678</v>
+        <v>0.107216</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="S25" s="29" t="n">
         <v>2</v>
@@ -7715,7 +7827,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-wc-mglz-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -7756,32 +7868,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>TheMongolz</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Wildcard</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -7834,7 +7946,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:46.102307Z</t>
+          <t>2026-07-26T18:27:02.997218Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -7844,13 +7956,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.588235</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.62963</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -7884,22 +7996,22 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>59899b82acff46b4</t>
+          <t>b11ee695a5af413c</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T15:00:00Z</t>
+          <t>2026-07-27T15:30:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>61671</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -7909,12 +8021,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -7934,23 +8046,23 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>178</v>
+        <v>-194</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2.78</v>
+        <v>1.515464</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.659864</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.786851</v>
+        <v>0.735192</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.427139</v>
+        <v>0.07532800000000001</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="S26" s="29" t="n">
         <v>2</v>
@@ -7976,7 +8088,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-odk-ldp-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-brute-navij-2026-07-27).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8017,32 +8129,32 @@
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>largadosypelados</t>
+          <t>NAVI Junior</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>ODDIK</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8095,7 +8207,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:46.942100Z</t>
+          <t>2026-07-26T18:27:15.414223Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8105,13 +8217,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>178</v>
+        <v>-194</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2.78</v>
+        <v>1.515464</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.659864</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8145,22 +8257,22 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>560429622c8e4af9</t>
+          <t>823fa2a1e1614c00</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T15:30:00Z</t>
+          <t>2026-07-27T16:30:00Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>61480</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8170,12 +8282,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8195,26 +8307,26 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.558205</v>
+        <v>0.659512</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.082083</v>
+        <v>0.050137</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -8237,7 +8349,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-aimc-sle-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8278,32 +8390,32 @@
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>sleepers</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>aimclub</t>
+          <t>Brute</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -8356,7 +8468,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:48.845751Z</t>
+          <t>2026-07-26T18:27:16.097256Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8366,13 +8478,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -8406,22 +8518,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>40692918b0c94676</t>
+          <t>25355d2eaef14496</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T16:00:00Z</t>
+          <t>2026-07-27T17:00:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>60794</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -8431,12 +8543,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -8446,7 +8558,7 @@
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J28" s="25" t="n"/>
@@ -8456,26 +8568,26 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.13</v>
+        <v>2.78</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.359712</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.665479</v>
+        <v>0.573171</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.195995</v>
+        <v>0.213459</v>
       </c>
       <c r="R28" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
@@ -8498,7 +8610,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-mgc-nip-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -8539,32 +8651,32 @@
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>NIP</t>
+          <t>HATERS</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>magic</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -8617,7 +8729,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:49.664310Z</t>
+          <t>2026-07-26T18:27:16.598199Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -8627,13 +8739,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>2.13</v>
+        <v>2.78</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.359712</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -8667,22 +8779,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>18212168114f4d40</t>
+          <t>05bd5a76938042df</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
+          <t>2026-07-26T18:27:18.671145Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T17:00:00Z</t>
+          <t>2026-07-27T17:00:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>62237</t>
+          <t>60795</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -8692,12 +8804,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -8726,14 +8838,14 @@
         <v>0.619772</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.700097</v>
+        <v>0.70196</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.08032499999999999</v>
+        <v>0.082188</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S29" s="29" t="n">
         <v>2</v>
@@ -8759,7 +8871,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-hon-pg-2026-07-26).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -8800,32 +8912,32 @@
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>Privateer Gaming</t>
+          <t>Falcons Force</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -8878,7 +8990,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T12:49:51.560831Z</t>
+          <t>2026-07-26T18:27:17.140917Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -8925,3921 +9037,6 @@
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>d9e51b7109cb4f98</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C30" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="inlineStr">
-        <is>
-          <t>61034</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F30" s="24" t="inlineStr">
-        <is>
-          <t>Atreides</t>
-        </is>
-      </c>
-      <c r="G30" s="24" t="inlineStr">
-        <is>
-          <t>Esport Academy Copenhagen</t>
-        </is>
-      </c>
-      <c r="H30" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I30" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L30" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M30" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N30" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O30" s="28" t="n">
-        <v>0.527474</v>
-      </c>
-      <c r="P30" s="28" t="n"/>
-      <c r="Q30" s="28" t="n">
-        <v>-0.052358</v>
-      </c>
-      <c r="R30" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T30" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U30" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
-      <c r="Y30" s="25" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="28" t="n"/>
-      <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
-      <c r="AE30" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-eac-atr-2026-07-26).</t>
-        </is>
-      </c>
-      <c r="AF30" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG30" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH30" s="24" t="n"/>
-      <c r="AI30" s="31" t="n"/>
-      <c r="AJ30" s="31" t="n"/>
-      <c r="AK30" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL30" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM30" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN30" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO30" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP30" s="24" t="inlineStr">
-        <is>
-          <t>Atreides</t>
-        </is>
-      </c>
-      <c r="AQ30" s="24" t="inlineStr">
-        <is>
-          <t>Atreides</t>
-        </is>
-      </c>
-      <c r="AR30" s="24" t="inlineStr">
-        <is>
-          <t>Atreides</t>
-        </is>
-      </c>
-      <c r="AS30" s="24" t="inlineStr">
-        <is>
-          <t>Esport Academy Copenhagen</t>
-        </is>
-      </c>
-      <c r="AT30" s="24" t="inlineStr">
-        <is>
-          <t>Esport Academy Copenhagen</t>
-        </is>
-      </c>
-      <c r="AU30" s="24" t="inlineStr">
-        <is>
-          <t>Esport Academy Copenhagen</t>
-        </is>
-      </c>
-      <c r="AV30" s="24" t="n"/>
-      <c r="AW30" s="24" t="n"/>
-      <c r="AX30" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY30" s="24" t="n"/>
-      <c r="AZ30" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA30" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB30" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC30" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD30" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE30" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF30" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG30" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH30" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:49:52.386615Z</t>
-        </is>
-      </c>
-      <c r="BI30" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ30" s="25" t="n"/>
-      <c r="BK30" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL30" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM30" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN30" s="28" t="n"/>
-      <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
-      <c r="BR30" s="28" t="n"/>
-      <c r="BS30" s="28" t="n"/>
-      <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
-      <c r="BV30" s="29" t="n"/>
-      <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n"/>
-      <c r="BY30" s="27" t="n"/>
-      <c r="BZ30" s="24" t="n"/>
-      <c r="CA30" s="31" t="n"/>
-      <c r="CB30" s="24" t="n"/>
-      <c r="CC30" s="24" t="n"/>
-      <c r="CD30" s="24" t="n"/>
-      <c r="CE30" s="24" t="n"/>
-      <c r="CF30" s="24" t="n"/>
-      <c r="CG30" s="24" t="n"/>
-      <c r="CH30" s="24" t="n"/>
-      <c r="CI30" s="24" t="n"/>
-      <c r="CJ30" s="24" t="n"/>
-      <c r="CK30" s="24" t="n"/>
-      <c r="CL30" s="24" t="n"/>
-      <c r="CM30" s="24" t="n"/>
-      <c r="CN30" s="24" t="n"/>
-      <c r="CO30" s="24" t="n"/>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
-        <is>
-          <t>af60000a899b4f20</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>61038</t>
-        </is>
-      </c>
-      <c r="E31" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F31" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="G31" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="H31" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I31" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L31" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M31" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N31" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O31" s="28" t="n">
-        <v>0.758379</v>
-      </c>
-      <c r="P31" s="28" t="n"/>
-      <c r="Q31" s="28" t="n">
-        <v>0.27761</v>
-      </c>
-      <c r="R31" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S31" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U31" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
-      <c r="Y31" s="25" t="n"/>
-      <c r="Z31" s="26" t="n"/>
-      <c r="AA31" s="28" t="n"/>
-      <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
-      <c r="AE31" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-lav-btf-2026-07-26).</t>
-        </is>
-      </c>
-      <c r="AF31" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG31" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH31" s="24" t="n"/>
-      <c r="AI31" s="31" t="n"/>
-      <c r="AJ31" s="31" t="n"/>
-      <c r="AK31" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL31" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM31" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN31" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO31" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP31" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AQ31" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AR31" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AS31" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="AT31" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="AU31" s="24" t="inlineStr">
-        <is>
-          <t>Lavked</t>
-        </is>
-      </c>
-      <c r="AV31" s="24" t="n"/>
-      <c r="AW31" s="24" t="n"/>
-      <c r="AX31" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY31" s="24" t="n"/>
-      <c r="AZ31" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA31" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB31" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC31" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD31" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE31" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF31" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG31" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH31" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:49:53.215216Z</t>
-        </is>
-      </c>
-      <c r="BI31" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ31" s="25" t="n"/>
-      <c r="BK31" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL31" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM31" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN31" s="28" t="n"/>
-      <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
-      <c r="BR31" s="28" t="n"/>
-      <c r="BS31" s="28" t="n"/>
-      <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
-      <c r="BV31" s="29" t="n"/>
-      <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n"/>
-      <c r="BY31" s="27" t="n"/>
-      <c r="BZ31" s="24" t="n"/>
-      <c r="CA31" s="31" t="n"/>
-      <c r="CB31" s="24" t="n"/>
-      <c r="CC31" s="24" t="n"/>
-      <c r="CD31" s="24" t="n"/>
-      <c r="CE31" s="24" t="n"/>
-      <c r="CF31" s="24" t="n"/>
-      <c r="CG31" s="24" t="n"/>
-      <c r="CH31" s="24" t="n"/>
-      <c r="CI31" s="24" t="n"/>
-      <c r="CJ31" s="24" t="n"/>
-      <c r="CK31" s="24" t="n"/>
-      <c r="CL31" s="24" t="n"/>
-      <c r="CM31" s="24" t="n"/>
-      <c r="CN31" s="24" t="n"/>
-      <c r="CO31" s="24" t="n"/>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
-        <is>
-          <t>7dae7b196b1b44a2</t>
-        </is>
-      </c>
-      <c r="B32" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:15:00Z</t>
-        </is>
-      </c>
-      <c r="D32" s="24" t="inlineStr">
-        <is>
-          <t>61472</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F32" s="24" t="inlineStr">
-        <is>
-          <t>mellren</t>
-        </is>
-      </c>
-      <c r="G32" s="24" t="inlineStr">
-        <is>
-          <t>A Great Chaos</t>
-        </is>
-      </c>
-      <c r="H32" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I32" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L32" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M32" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N32" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O32" s="28" t="n">
-        <v>0.703286</v>
-      </c>
-      <c r="P32" s="28" t="n"/>
-      <c r="Q32" s="28" t="n">
-        <v>0.012884</v>
-      </c>
-      <c r="R32" s="26" t="n">
-        <v>26</v>
-      </c>
-      <c r="S32" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U32" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V32" s="24" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
-      <c r="Y32" s="25" t="n"/>
-      <c r="Z32" s="26" t="n"/>
-      <c r="AA32" s="28" t="n"/>
-      <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
-      <c r="AD32" s="24" t="n"/>
-      <c r="AE32" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-agc-mel-2026-07-26).</t>
-        </is>
-      </c>
-      <c r="AF32" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG32" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH32" s="24" t="n"/>
-      <c r="AI32" s="31" t="n"/>
-      <c r="AJ32" s="31" t="n"/>
-      <c r="AK32" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL32" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM32" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN32" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO32" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP32" s="24" t="inlineStr">
-        <is>
-          <t>mellren</t>
-        </is>
-      </c>
-      <c r="AQ32" s="24" t="inlineStr">
-        <is>
-          <t>mellren</t>
-        </is>
-      </c>
-      <c r="AR32" s="24" t="inlineStr">
-        <is>
-          <t>mellren</t>
-        </is>
-      </c>
-      <c r="AS32" s="24" t="inlineStr">
-        <is>
-          <t>A Great Chaos</t>
-        </is>
-      </c>
-      <c r="AT32" s="24" t="inlineStr">
-        <is>
-          <t>A Great Chaos</t>
-        </is>
-      </c>
-      <c r="AU32" s="24" t="inlineStr">
-        <is>
-          <t>A Great Chaos</t>
-        </is>
-      </c>
-      <c r="AV32" s="24" t="n"/>
-      <c r="AW32" s="24" t="n"/>
-      <c r="AX32" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY32" s="24" t="n"/>
-      <c r="AZ32" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA32" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB32" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC32" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD32" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE32" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF32" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG32" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH32" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:49:56.663548Z</t>
-        </is>
-      </c>
-      <c r="BI32" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ32" s="25" t="n"/>
-      <c r="BK32" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL32" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM32" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN32" s="28" t="n"/>
-      <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
-      <c r="BR32" s="28" t="n"/>
-      <c r="BS32" s="28" t="n"/>
-      <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
-      <c r="BV32" s="29" t="n"/>
-      <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n"/>
-      <c r="BY32" s="27" t="n"/>
-      <c r="BZ32" s="24" t="n"/>
-      <c r="CA32" s="31" t="n"/>
-      <c r="CB32" s="24" t="n"/>
-      <c r="CC32" s="24" t="n"/>
-      <c r="CD32" s="24" t="n"/>
-      <c r="CE32" s="24" t="n"/>
-      <c r="CF32" s="24" t="n"/>
-      <c r="CG32" s="24" t="n"/>
-      <c r="CH32" s="24" t="n"/>
-      <c r="CI32" s="24" t="n"/>
-      <c r="CJ32" s="24" t="n"/>
-      <c r="CK32" s="24" t="n"/>
-      <c r="CL32" s="24" t="n"/>
-      <c r="CM32" s="24" t="n"/>
-      <c r="CN32" s="24" t="n"/>
-      <c r="CO32" s="24" t="n"/>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>f5b2eb857251441c</t>
-        </is>
-      </c>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D33" s="24" t="inlineStr">
-        <is>
-          <t>60702</t>
-        </is>
-      </c>
-      <c r="E33" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F33" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="G33" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="H33" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I33" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J33" s="25" t="n"/>
-      <c r="K33" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L33" s="26" t="n">
-        <v>163</v>
-      </c>
-      <c r="M33" s="27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N33" s="28" t="n">
-        <v>0.380228</v>
-      </c>
-      <c r="O33" s="28" t="n">
-        <v>0.607321</v>
-      </c>
-      <c r="P33" s="28" t="n"/>
-      <c r="Q33" s="28" t="n">
-        <v>0.227093</v>
-      </c>
-      <c r="R33" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S33" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T33" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U33" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V33" s="24" t="n"/>
-      <c r="W33" s="26" t="n"/>
-      <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="25" t="n"/>
-      <c r="Z33" s="26" t="n"/>
-      <c r="AA33" s="28" t="n"/>
-      <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n"/>
-      <c r="AD33" s="24" t="n"/>
-      <c r="AE33" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-erx-ent-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF33" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG33" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH33" s="24" t="n"/>
-      <c r="AI33" s="31" t="n"/>
-      <c r="AJ33" s="31" t="n"/>
-      <c r="AK33" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL33" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM33" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN33" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO33" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP33" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AQ33" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AR33" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AS33" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AT33" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AU33" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUSTEC</t>
-        </is>
-      </c>
-      <c r="AV33" s="24" t="n"/>
-      <c r="AW33" s="24" t="n"/>
-      <c r="AX33" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY33" s="24" t="n"/>
-      <c r="AZ33" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA33" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB33" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC33" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD33" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE33" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF33" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG33" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH33" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:49:59.220544Z</t>
-        </is>
-      </c>
-      <c r="BI33" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ33" s="25" t="n"/>
-      <c r="BK33" s="26" t="n">
-        <v>163</v>
-      </c>
-      <c r="BL33" s="27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BM33" s="28" t="n">
-        <v>0.380228</v>
-      </c>
-      <c r="BN33" s="28" t="n"/>
-      <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
-      <c r="BR33" s="28" t="n"/>
-      <c r="BS33" s="28" t="n"/>
-      <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
-      <c r="BV33" s="29" t="n"/>
-      <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n"/>
-      <c r="BY33" s="27" t="n"/>
-      <c r="BZ33" s="24" t="n"/>
-      <c r="CA33" s="31" t="n"/>
-      <c r="CB33" s="24" t="n"/>
-      <c r="CC33" s="24" t="n"/>
-      <c r="CD33" s="24" t="n"/>
-      <c r="CE33" s="24" t="n"/>
-      <c r="CF33" s="24" t="n"/>
-      <c r="CG33" s="24" t="n"/>
-      <c r="CH33" s="24" t="n"/>
-      <c r="CI33" s="24" t="n"/>
-      <c r="CJ33" s="24" t="n"/>
-      <c r="CK33" s="24" t="n"/>
-      <c r="CL33" s="24" t="n"/>
-      <c r="CM33" s="24" t="n"/>
-      <c r="CN33" s="24" t="n"/>
-      <c r="CO33" s="24" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>8baf57eda3434730</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D34" s="24" t="inlineStr">
-        <is>
-          <t>60732</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F34" s="24" t="inlineStr">
-        <is>
-          <t>Noir Verse</t>
-        </is>
-      </c>
-      <c r="G34" s="24" t="inlineStr">
-        <is>
-          <t>ASTRAL</t>
-        </is>
-      </c>
-      <c r="H34" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I34" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L34" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="M34" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="N34" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="O34" s="28" t="n">
-        <v>0.736846</v>
-      </c>
-      <c r="P34" s="28" t="n"/>
-      <c r="Q34" s="28" t="n">
-        <v>0.107216</v>
-      </c>
-      <c r="R34" s="26" t="n">
-        <v>74</v>
-      </c>
-      <c r="S34" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U34" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V34" s="24" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="25" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="28" t="n"/>
-      <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
-      <c r="AD34" s="24" t="n"/>
-      <c r="AE34" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF34" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG34" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH34" s="24" t="n"/>
-      <c r="AI34" s="31" t="n"/>
-      <c r="AJ34" s="31" t="n"/>
-      <c r="AK34" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL34" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM34" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN34" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO34" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP34" s="24" t="inlineStr">
-        <is>
-          <t>Noir Verse</t>
-        </is>
-      </c>
-      <c r="AQ34" s="24" t="inlineStr">
-        <is>
-          <t>Noir Verse</t>
-        </is>
-      </c>
-      <c r="AR34" s="24" t="inlineStr">
-        <is>
-          <t>Noir Verse</t>
-        </is>
-      </c>
-      <c r="AS34" s="24" t="inlineStr">
-        <is>
-          <t>ASTRAL</t>
-        </is>
-      </c>
-      <c r="AT34" s="24" t="inlineStr">
-        <is>
-          <t>ASTRAL</t>
-        </is>
-      </c>
-      <c r="AU34" s="24" t="inlineStr">
-        <is>
-          <t>ASTRAL</t>
-        </is>
-      </c>
-      <c r="AV34" s="24" t="n"/>
-      <c r="AW34" s="24" t="n"/>
-      <c r="AX34" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY34" s="24" t="n"/>
-      <c r="AZ34" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA34" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB34" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC34" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD34" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE34" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF34" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG34" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH34" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:00.851568Z</t>
-        </is>
-      </c>
-      <c r="BI34" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ34" s="25" t="n"/>
-      <c r="BK34" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="BL34" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="BM34" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="BN34" s="28" t="n"/>
-      <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
-      <c r="BR34" s="28" t="n"/>
-      <c r="BS34" s="28" t="n"/>
-      <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
-      <c r="BV34" s="29" t="n"/>
-      <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
-      <c r="BZ34" s="24" t="n"/>
-      <c r="CA34" s="31" t="n"/>
-      <c r="CB34" s="24" t="n"/>
-      <c r="CC34" s="24" t="n"/>
-      <c r="CD34" s="24" t="n"/>
-      <c r="CE34" s="24" t="n"/>
-      <c r="CF34" s="24" t="n"/>
-      <c r="CG34" s="24" t="n"/>
-      <c r="CH34" s="24" t="n"/>
-      <c r="CI34" s="24" t="n"/>
-      <c r="CJ34" s="24" t="n"/>
-      <c r="CK34" s="24" t="n"/>
-      <c r="CL34" s="24" t="n"/>
-      <c r="CM34" s="24" t="n"/>
-      <c r="CN34" s="24" t="n"/>
-      <c r="CO34" s="24" t="n"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="24" t="inlineStr">
-        <is>
-          <t>5ed1eac63e1d4e99</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>60729</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F35" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="G35" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="H35" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I35" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J35" s="25" t="n"/>
-      <c r="K35" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L35" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M35" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N35" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O35" s="28" t="n">
-        <v>0.539211</v>
-      </c>
-      <c r="P35" s="28" t="n"/>
-      <c r="Q35" s="28" t="n">
-        <v>-0.060789</v>
-      </c>
-      <c r="R35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U35" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V35" s="24" t="n"/>
-      <c r="W35" s="26" t="n"/>
-      <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="25" t="n"/>
-      <c r="Z35" s="26" t="n"/>
-      <c r="AA35" s="28" t="n"/>
-      <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n"/>
-      <c r="AD35" s="24" t="n"/>
-      <c r="AE35" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-unity-mta-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF35" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG35" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH35" s="24" t="n"/>
-      <c r="AI35" s="31" t="n"/>
-      <c r="AJ35" s="31" t="n"/>
-      <c r="AK35" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL35" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM35" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN35" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO35" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP35" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AQ35" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AR35" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AS35" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="AT35" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="AU35" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="AV35" s="24" t="n"/>
-      <c r="AW35" s="24" t="n"/>
-      <c r="AX35" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY35" s="24" t="n"/>
-      <c r="AZ35" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA35" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB35" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC35" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD35" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE35" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF35" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG35" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH35" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:01.643224Z</t>
-        </is>
-      </c>
-      <c r="BI35" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ35" s="25" t="n"/>
-      <c r="BK35" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL35" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM35" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN35" s="28" t="n"/>
-      <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
-      <c r="BR35" s="28" t="n"/>
-      <c r="BS35" s="28" t="n"/>
-      <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
-      <c r="BV35" s="29" t="n"/>
-      <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n"/>
-      <c r="BY35" s="27" t="n"/>
-      <c r="BZ35" s="24" t="n"/>
-      <c r="CA35" s="31" t="n"/>
-      <c r="CB35" s="24" t="n"/>
-      <c r="CC35" s="24" t="n"/>
-      <c r="CD35" s="24" t="n"/>
-      <c r="CE35" s="24" t="n"/>
-      <c r="CF35" s="24" t="n"/>
-      <c r="CG35" s="24" t="n"/>
-      <c r="CH35" s="24" t="n"/>
-      <c r="CI35" s="24" t="n"/>
-      <c r="CJ35" s="24" t="n"/>
-      <c r="CK35" s="24" t="n"/>
-      <c r="CL35" s="24" t="n"/>
-      <c r="CM35" s="24" t="n"/>
-      <c r="CN35" s="24" t="n"/>
-      <c r="CO35" s="24" t="n"/>
-    </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>50783c88f8a24829</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>60748</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L36" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="N36" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="O36" s="28" t="n">
-        <v>0.531101</v>
-      </c>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n">
-        <v>-0.14941</v>
-      </c>
-      <c r="R36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U36" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="28" t="n"/>
-      <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
-      <c r="AE36" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-bpl-misa-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF36" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG36" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH36" s="24" t="n"/>
-      <c r="AI36" s="31" t="n"/>
-      <c r="AJ36" s="31" t="n"/>
-      <c r="AK36" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL36" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM36" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN36" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO36" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP36" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="AQ36" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="AR36" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="AS36" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="AT36" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="AU36" s="24" t="inlineStr">
-        <is>
-          <t>Black Phoenix</t>
-        </is>
-      </c>
-      <c r="AV36" s="24" t="n"/>
-      <c r="AW36" s="24" t="n"/>
-      <c r="AX36" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY36" s="24" t="n"/>
-      <c r="AZ36" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA36" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB36" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD36" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:05.947250Z</t>
-        </is>
-      </c>
-      <c r="BI36" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ36" s="25" t="n"/>
-      <c r="BK36" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="BL36" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="BM36" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="BN36" s="28" t="n"/>
-      <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
-      <c r="BR36" s="28" t="n"/>
-      <c r="BS36" s="28" t="n"/>
-      <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
-      <c r="BV36" s="29" t="n"/>
-      <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
-      <c r="BZ36" s="24" t="n"/>
-      <c r="CA36" s="31" t="n"/>
-      <c r="CB36" s="24" t="n"/>
-      <c r="CC36" s="24" t="n"/>
-      <c r="CD36" s="24" t="n"/>
-      <c r="CE36" s="24" t="n"/>
-      <c r="CF36" s="24" t="n"/>
-      <c r="CG36" s="24" t="n"/>
-      <c r="CH36" s="24" t="n"/>
-      <c r="CI36" s="24" t="n"/>
-      <c r="CJ36" s="24" t="n"/>
-      <c r="CK36" s="24" t="n"/>
-      <c r="CL36" s="24" t="n"/>
-      <c r="CM36" s="24" t="n"/>
-      <c r="CN36" s="24" t="n"/>
-      <c r="CO36" s="24" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>be6605fbc88841cd</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T15:30:00Z</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>60764</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="G37" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="H37" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I37" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J37" s="25" t="n"/>
-      <c r="K37" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L37" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="M37" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="N37" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="O37" s="28" t="n">
-        <v>0.735192</v>
-      </c>
-      <c r="P37" s="28" t="n"/>
-      <c r="Q37" s="28" t="n">
-        <v>0.07532800000000001</v>
-      </c>
-      <c r="R37" s="26" t="n">
-        <v>58</v>
-      </c>
-      <c r="S37" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T37" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U37" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="26" t="n"/>
-      <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
-      <c r="Z37" s="26" t="n"/>
-      <c r="AA37" s="28" t="n"/>
-      <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
-      <c r="AD37" s="24" t="n"/>
-      <c r="AE37" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-brute-navij-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF37" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG37" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH37" s="24" t="n"/>
-      <c r="AI37" s="31" t="n"/>
-      <c r="AJ37" s="31" t="n"/>
-      <c r="AK37" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL37" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM37" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN37" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO37" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP37" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="AQ37" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="AR37" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="AS37" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="AT37" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="AU37" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="AV37" s="24" t="n"/>
-      <c r="AW37" s="24" t="n"/>
-      <c r="AX37" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY37" s="24" t="n"/>
-      <c r="AZ37" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA37" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB37" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC37" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD37" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE37" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF37" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG37" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:08.444139Z</t>
-        </is>
-      </c>
-      <c r="BI37" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ37" s="25" t="n"/>
-      <c r="BK37" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="BL37" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="BM37" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="BN37" s="28" t="n"/>
-      <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
-      <c r="BR37" s="28" t="n"/>
-      <c r="BS37" s="28" t="n"/>
-      <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
-      <c r="BV37" s="29" t="n"/>
-      <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
-      <c r="BZ37" s="24" t="n"/>
-      <c r="CA37" s="31" t="n"/>
-      <c r="CB37" s="24" t="n"/>
-      <c r="CC37" s="24" t="n"/>
-      <c r="CD37" s="24" t="n"/>
-      <c r="CE37" s="24" t="n"/>
-      <c r="CF37" s="24" t="n"/>
-      <c r="CG37" s="24" t="n"/>
-      <c r="CH37" s="24" t="n"/>
-      <c r="CI37" s="24" t="n"/>
-      <c r="CJ37" s="24" t="n"/>
-      <c r="CK37" s="24" t="n"/>
-      <c r="CL37" s="24" t="n"/>
-      <c r="CM37" s="24" t="n"/>
-      <c r="CN37" s="24" t="n"/>
-      <c r="CO37" s="24" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>61e3eea0edd34b41</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T16:30:00Z</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>60788</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L38" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N38" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O38" s="28" t="n">
-        <v>0.659512</v>
-      </c>
-      <c r="P38" s="28" t="n"/>
-      <c r="Q38" s="28" t="n">
-        <v>0.050137</v>
-      </c>
-      <c r="R38" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="S38" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U38" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
-      <c r="Z38" s="26" t="n"/>
-      <c r="AA38" s="28" t="n"/>
-      <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
-      <c r="AE38" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF38" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG38" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH38" s="24" t="n"/>
-      <c r="AI38" s="31" t="n"/>
-      <c r="AJ38" s="31" t="n"/>
-      <c r="AK38" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL38" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM38" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN38" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO38" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP38" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="AQ38" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="AR38" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="AS38" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="AT38" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="AU38" s="24" t="inlineStr">
-        <is>
-          <t>Brute</t>
-        </is>
-      </c>
-      <c r="AV38" s="24" t="n"/>
-      <c r="AW38" s="24" t="n"/>
-      <c r="AX38" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY38" s="24" t="n"/>
-      <c r="AZ38" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA38" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB38" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD38" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:09.212122Z</t>
-        </is>
-      </c>
-      <c r="BI38" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ38" s="25" t="n"/>
-      <c r="BK38" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL38" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM38" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN38" s="28" t="n"/>
-      <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
-      <c r="BR38" s="28" t="n"/>
-      <c r="BS38" s="28" t="n"/>
-      <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
-      <c r="BV38" s="29" t="n"/>
-      <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
-      <c r="BZ38" s="24" t="n"/>
-      <c r="CA38" s="31" t="n"/>
-      <c r="CB38" s="24" t="n"/>
-      <c r="CC38" s="24" t="n"/>
-      <c r="CD38" s="24" t="n"/>
-      <c r="CE38" s="24" t="n"/>
-      <c r="CF38" s="24" t="n"/>
-      <c r="CG38" s="24" t="n"/>
-      <c r="CH38" s="24" t="n"/>
-      <c r="CI38" s="24" t="n"/>
-      <c r="CJ38" s="24" t="n"/>
-      <c r="CK38" s="24" t="n"/>
-      <c r="CL38" s="24" t="n"/>
-      <c r="CM38" s="24" t="n"/>
-      <c r="CN38" s="24" t="n"/>
-      <c r="CO38" s="24" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>1783410eb2224c7b</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>60795</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>Bebop</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L39" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N39" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O39" s="28" t="n">
-        <v>0.70196</v>
-      </c>
-      <c r="P39" s="28" t="n"/>
-      <c r="Q39" s="28" t="n">
-        <v>0.082188</v>
-      </c>
-      <c r="R39" s="26" t="n">
-        <v>61</v>
-      </c>
-      <c r="S39" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U39" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="28" t="n"/>
-      <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
-      <c r="AD39" s="24" t="n"/>
-      <c r="AE39" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF39" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG39" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH39" s="24" t="n"/>
-      <c r="AI39" s="31" t="n"/>
-      <c r="AJ39" s="31" t="n"/>
-      <c r="AK39" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL39" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM39" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN39" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO39" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP39" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="AQ39" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="AR39" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="AS39" s="24" t="inlineStr">
-        <is>
-          <t>Bebop</t>
-        </is>
-      </c>
-      <c r="AT39" s="24" t="inlineStr">
-        <is>
-          <t>Bebop</t>
-        </is>
-      </c>
-      <c r="AU39" s="24" t="inlineStr">
-        <is>
-          <t>Bebop</t>
-        </is>
-      </c>
-      <c r="AV39" s="24" t="n"/>
-      <c r="AW39" s="24" t="n"/>
-      <c r="AX39" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY39" s="24" t="n"/>
-      <c r="AZ39" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA39" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB39" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD39" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:09.997048Z</t>
-        </is>
-      </c>
-      <c r="BI39" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ39" s="25" t="n"/>
-      <c r="BK39" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL39" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM39" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN39" s="28" t="n"/>
-      <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
-      <c r="BR39" s="28" t="n"/>
-      <c r="BS39" s="28" t="n"/>
-      <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
-      <c r="BV39" s="29" t="n"/>
-      <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
-      <c r="BZ39" s="24" t="n"/>
-      <c r="CA39" s="31" t="n"/>
-      <c r="CB39" s="24" t="n"/>
-      <c r="CC39" s="24" t="n"/>
-      <c r="CD39" s="24" t="n"/>
-      <c r="CE39" s="24" t="n"/>
-      <c r="CF39" s="24" t="n"/>
-      <c r="CG39" s="24" t="n"/>
-      <c r="CH39" s="24" t="n"/>
-      <c r="CI39" s="24" t="n"/>
-      <c r="CJ39" s="24" t="n"/>
-      <c r="CK39" s="24" t="n"/>
-      <c r="CL39" s="24" t="n"/>
-      <c r="CM39" s="24" t="n"/>
-      <c r="CN39" s="24" t="n"/>
-      <c r="CO39" s="24" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>f0f96c93fc0a40a9</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>60794</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I40" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L40" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="M40" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="N40" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="O40" s="28" t="n">
-        <v>0.573171</v>
-      </c>
-      <c r="P40" s="28" t="n"/>
-      <c r="Q40" s="28" t="n">
-        <v>0.213459</v>
-      </c>
-      <c r="R40" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S40" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U40" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="25" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
-      <c r="AD40" s="24" t="n"/>
-      <c r="AE40" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF40" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG40" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH40" s="24" t="n"/>
-      <c r="AI40" s="31" t="n"/>
-      <c r="AJ40" s="31" t="n"/>
-      <c r="AK40" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL40" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM40" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN40" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO40" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP40" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AQ40" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AR40" s="24" t="inlineStr">
-        <is>
-          <t>HATERS</t>
-        </is>
-      </c>
-      <c r="AS40" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="AT40" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="AU40" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="AV40" s="24" t="n"/>
-      <c r="AW40" s="24" t="n"/>
-      <c r="AX40" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY40" s="24" t="n"/>
-      <c r="AZ40" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA40" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB40" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD40" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:10.787657Z</t>
-        </is>
-      </c>
-      <c r="BI40" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ40" s="25" t="n"/>
-      <c r="BK40" s="26" t="n">
-        <v>178</v>
-      </c>
-      <c r="BL40" s="27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BM40" s="28" t="n">
-        <v>0.359712</v>
-      </c>
-      <c r="BN40" s="28" t="n"/>
-      <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
-      <c r="BR40" s="28" t="n"/>
-      <c r="BS40" s="28" t="n"/>
-      <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="25" t="n"/>
-      <c r="BV40" s="29" t="n"/>
-      <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="30" t="n"/>
-      <c r="BY40" s="27" t="n"/>
-      <c r="BZ40" s="24" t="n"/>
-      <c r="CA40" s="31" t="n"/>
-      <c r="CB40" s="24" t="n"/>
-      <c r="CC40" s="24" t="n"/>
-      <c r="CD40" s="24" t="n"/>
-      <c r="CE40" s="24" t="n"/>
-      <c r="CF40" s="24" t="n"/>
-      <c r="CG40" s="24" t="n"/>
-      <c r="CH40" s="24" t="n"/>
-      <c r="CI40" s="24" t="n"/>
-      <c r="CJ40" s="24" t="n"/>
-      <c r="CK40" s="24" t="n"/>
-      <c r="CL40" s="24" t="n"/>
-      <c r="CM40" s="24" t="n"/>
-      <c r="CN40" s="24" t="n"/>
-      <c r="CO40" s="24" t="n"/>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>68214b242dbe452e</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:13.208687Z</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T17:30:00Z</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>60805</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N41" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O41" s="28" t="n">
-        <v>0.55859</v>
-      </c>
-      <c r="P41" s="28" t="n"/>
-      <c r="Q41" s="28" t="n">
-        <v>-0.050785</v>
-      </c>
-      <c r="R41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U41" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="28" t="n"/>
-      <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
-      <c r="AE41" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-navij-mouzn-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF41" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG41" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH41" s="24" t="n"/>
-      <c r="AI41" s="31" t="n"/>
-      <c r="AJ41" s="31" t="n"/>
-      <c r="AK41" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL41" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN41" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO41" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP41" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="AQ41" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="AR41" s="24" t="inlineStr">
-        <is>
-          <t>MOUZ NXT</t>
-        </is>
-      </c>
-      <c r="AS41" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="AT41" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="AU41" s="24" t="inlineStr">
-        <is>
-          <t>NAVI Junior</t>
-        </is>
-      </c>
-      <c r="AV41" s="24" t="n"/>
-      <c r="AW41" s="24" t="n"/>
-      <c r="AX41" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY41" s="24" t="n"/>
-      <c r="AZ41" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA41" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BB41" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD41" s="24" t="inlineStr">
-        <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
-        </is>
-      </c>
-      <c r="BE41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:11.590131Z</t>
-        </is>
-      </c>
-      <c r="BI41" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ41" s="25" t="n"/>
-      <c r="BK41" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL41" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM41" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN41" s="28" t="n"/>
-      <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="28" t="n"/>
-      <c r="BS41" s="28" t="n"/>
-      <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
-      <c r="BV41" s="29" t="n"/>
-      <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
-      <c r="BZ41" s="24" t="n"/>
-      <c r="CA41" s="31" t="n"/>
-      <c r="CB41" s="24" t="n"/>
-      <c r="CC41" s="24" t="n"/>
-      <c r="CD41" s="24" t="n"/>
-      <c r="CE41" s="24" t="n"/>
-      <c r="CF41" s="24" t="n"/>
-      <c r="CG41" s="24" t="n"/>
-      <c r="CH41" s="24" t="n"/>
-      <c r="CI41" s="24" t="n"/>
-      <c r="CJ41" s="24" t="n"/>
-      <c r="CK41" s="24" t="n"/>
-      <c r="CL41" s="24" t="n"/>
-      <c r="CM41" s="24" t="n"/>
-      <c r="CN41" s="24" t="n"/>
-      <c r="CO41" s="24" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>e7c15658496b44c8</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:45.242095Z</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>60136</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="M42" s="27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="N42" s="28" t="n">
-        <v>0.390625</v>
-      </c>
-      <c r="O42" s="28" t="n">
-        <v>0.7726229999999999</v>
-      </c>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="28" t="n">
-        <v>0.381998</v>
-      </c>
-      <c r="R42" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S42" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
-      <c r="AE42" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-bbl-navi-2026-07-26).</t>
-        </is>
-      </c>
-      <c r="AF42" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG42" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH42" s="24" t="n"/>
-      <c r="AI42" s="31" t="n"/>
-      <c r="AJ42" s="31" t="n"/>
-      <c r="AK42" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL42" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN42" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP42" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AQ42" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AR42" s="24" t="inlineStr">
-        <is>
-          <t>Natus Vincere</t>
-        </is>
-      </c>
-      <c r="AS42" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="AT42" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="AU42" s="24" t="inlineStr">
-        <is>
-          <t>BBL Esports</t>
-        </is>
-      </c>
-      <c r="AV42" s="24" t="n"/>
-      <c r="AW42" s="24" t="n"/>
-      <c r="AX42" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY42" s="24" t="n"/>
-      <c r="AZ42" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA42" s="24" t="inlineStr">
-        <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
-        </is>
-      </c>
-      <c r="BB42" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC42" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD42" s="24" t="inlineStr">
-        <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
-        </is>
-      </c>
-      <c r="BE42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG42" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:32.723645Z</t>
-        </is>
-      </c>
-      <c r="BI42" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ42" s="25" t="n"/>
-      <c r="BK42" s="26" t="n">
-        <v>156</v>
-      </c>
-      <c r="BL42" s="27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BM42" s="28" t="n">
-        <v>0.390625</v>
-      </c>
-      <c r="BN42" s="28" t="n"/>
-      <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
-      <c r="BS42" s="28" t="n"/>
-      <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
-      <c r="BV42" s="29" t="n"/>
-      <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
-      <c r="BZ42" s="24" t="n"/>
-      <c r="CA42" s="31" t="n"/>
-      <c r="CB42" s="24" t="n"/>
-      <c r="CC42" s="24" t="n"/>
-      <c r="CD42" s="24" t="n"/>
-      <c r="CE42" s="24" t="n"/>
-      <c r="CF42" s="24" t="n"/>
-      <c r="CG42" s="24" t="n"/>
-      <c r="CH42" s="24" t="n"/>
-      <c r="CI42" s="24" t="n"/>
-      <c r="CJ42" s="24" t="n"/>
-      <c r="CK42" s="24" t="n"/>
-      <c r="CL42" s="24" t="n"/>
-      <c r="CM42" s="24" t="n"/>
-      <c r="CN42" s="24" t="n"/>
-      <c r="CO42" s="24" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>b14286817f7e4bda</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:45.242095Z</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>60215</t>
-        </is>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I43" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J43" s="25" t="n"/>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M43" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N43" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O43" s="28" t="n">
-        <v>0.5200050000000001</v>
-      </c>
-      <c r="P43" s="28" t="n"/>
-      <c r="Q43" s="28" t="n">
-        <v>-0.05081</v>
-      </c>
-      <c r="R43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T43" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U43" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28" t="n"/>
-      <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
-      <c r="AE43" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-valorant-th-kc-2026-07-26).</t>
-        </is>
-      </c>
-      <c r="AF43" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG43" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH43" s="24" t="n"/>
-      <c r="AI43" s="31" t="n"/>
-      <c r="AJ43" s="31" t="n"/>
-      <c r="AK43" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL43" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM43" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN43" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO43" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP43" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp</t>
-        </is>
-      </c>
-      <c r="AQ43" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp</t>
-        </is>
-      </c>
-      <c r="AR43" s="24" t="inlineStr">
-        <is>
-          <t>Karmine Corp</t>
-        </is>
-      </c>
-      <c r="AS43" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AT43" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AU43" s="24" t="inlineStr">
-        <is>
-          <t>Team Heretics</t>
-        </is>
-      </c>
-      <c r="AV43" s="24" t="n"/>
-      <c r="AW43" s="24" t="n"/>
-      <c r="AX43" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY43" s="24" t="n"/>
-      <c r="AZ43" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA43" s="24" t="inlineStr">
-        <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
-        </is>
-      </c>
-      <c r="BB43" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC43" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD43" s="24" t="inlineStr">
-        <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
-        </is>
-      </c>
-      <c r="BE43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG43" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH43" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:33.517126Z</t>
-        </is>
-      </c>
-      <c r="BI43" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ43" s="25" t="n"/>
-      <c r="BK43" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL43" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM43" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN43" s="28" t="n"/>
-      <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
-      <c r="BR43" s="28" t="n"/>
-      <c r="BS43" s="28" t="n"/>
-      <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
-      <c r="BV43" s="29" t="n"/>
-      <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
-      <c r="BZ43" s="24" t="n"/>
-      <c r="CA43" s="31" t="n"/>
-      <c r="CB43" s="24" t="n"/>
-      <c r="CC43" s="24" t="n"/>
-      <c r="CD43" s="24" t="n"/>
-      <c r="CE43" s="24" t="n"/>
-      <c r="CF43" s="24" t="n"/>
-      <c r="CG43" s="24" t="n"/>
-      <c r="CH43" s="24" t="n"/>
-      <c r="CI43" s="24" t="n"/>
-      <c r="CJ43" s="24" t="n"/>
-      <c r="CK43" s="24" t="n"/>
-      <c r="CL43" s="24" t="n"/>
-      <c r="CM43" s="24" t="n"/>
-      <c r="CN43" s="24" t="n"/>
-      <c r="CO43" s="24" t="n"/>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>203f41dd4aae41cb</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:45.242095Z</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-27T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>60760</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports GC</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J44" s="25" t="n"/>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L44" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="M44" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N44" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="O44" s="28" t="n">
-        <v>0.5200050000000001</v>
-      </c>
-      <c r="P44" s="28" t="n"/>
-      <c r="Q44" s="28" t="n">
-        <v>0.079476</v>
-      </c>
-      <c r="R44" s="26" t="n">
-        <v>60</v>
-      </c>
-      <c r="S44" s="29" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T44" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U44" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="25" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="28" t="n"/>
-      <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
-      <c r="AE44" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-valorant-beg-hbs-2026-07-27).</t>
-        </is>
-      </c>
-      <c r="AF44" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG44" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH44" s="24" t="n"/>
-      <c r="AI44" s="31" t="n"/>
-      <c r="AJ44" s="31" t="n"/>
-      <c r="AK44" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL44" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM44" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN44" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO44" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP44" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AQ44" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AR44" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AS44" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports GC</t>
-        </is>
-      </c>
-      <c r="AT44" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports GC</t>
-        </is>
-      </c>
-      <c r="AU44" s="24" t="inlineStr">
-        <is>
-          <t>Barça eSports GC</t>
-        </is>
-      </c>
-      <c r="AV44" s="24" t="n"/>
-      <c r="AW44" s="24" t="n"/>
-      <c r="AX44" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY44" s="24" t="n"/>
-      <c r="AZ44" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA44" s="24" t="inlineStr">
-        <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
-        </is>
-      </c>
-      <c r="BB44" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC44" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD44" s="24" t="inlineStr">
-        <is>
-          <t>153b0db03af0303675f7eb2520b56d0fd86008f1bb62095f9881ea43a0124bb2</t>
-        </is>
-      </c>
-      <c r="BE44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG44" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH44" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-26T12:50:35.966755Z</t>
-        </is>
-      </c>
-      <c r="BI44" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ44" s="25" t="n"/>
-      <c r="BK44" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="BL44" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BM44" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="BN44" s="28" t="n"/>
-      <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
-      <c r="BR44" s="28" t="n"/>
-      <c r="BS44" s="28" t="n"/>
-      <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="25" t="n"/>
-      <c r="BV44" s="29" t="n"/>
-      <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="30" t="n"/>
-      <c r="BY44" s="27" t="n"/>
-      <c r="BZ44" s="24" t="n"/>
-      <c r="CA44" s="31" t="n"/>
-      <c r="CB44" s="24" t="n"/>
-      <c r="CC44" s="24" t="n"/>
-      <c r="CD44" s="24" t="n"/>
-      <c r="CE44" s="24" t="n"/>
-      <c r="CF44" s="24" t="n"/>
-      <c r="CG44" s="24" t="n"/>
-      <c r="CH44" s="24" t="n"/>
-      <c r="CI44" s="24" t="n"/>
-      <c r="CJ44" s="24" t="n"/>
-      <c r="CK44" s="24" t="n"/>
-      <c r="CL44" s="24" t="n"/>
-      <c r="CM44" s="24" t="n"/>
-      <c r="CN44" s="24" t="n"/>
-      <c r="CO44" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
